--- a/Day1_RAG_Components_Excel_Exercise.xlsx
+++ b/Day1_RAG_Components_Excel_Exercise.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tekframeworks1-my.sharepoint.com/personal/shonraj_ballae_tekframeworks_com/Documents/Training/ADP/ADP_AI_Training/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tekframeworks1-my.sharepoint.com/personal/shonraj_ballae_tekframeworks_com/Documents/Training/ADP/ADP_AI_Training/adp_applied_agent_engineering_lab_pack/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{B91978F9-4D0D-4CEB-A305-38D2EE17AF12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8984C931-9E2E-4EA2-A648-7220D39259BD}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{B91978F9-4D0D-4CEB-A305-38D2EE17AF12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C0C9AD4-798E-4112-B94C-F7659939C60A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D8384584-6B7E-4CAD-8076-2178920035E8}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="47">
   <si>
     <t xml:space="preserve"> Stage </t>
   </si>
@@ -75,9 +75,6 @@
   </si>
   <si>
     <t xml:space="preserve"> Data Ingestion </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  </t>
   </si>
   <si>
     <t xml:space="preserve"> Text Extraction </t>
@@ -646,229 +643,229 @@
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" t="s">
         <v>24</v>
       </c>
-      <c r="F4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>25</v>
-      </c>
-      <c r="I4" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="5" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" t="s">
         <v>27</v>
       </c>
-      <c r="E5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" t="s">
-        <v>28</v>
-      </c>
       <c r="I5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C7" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" t="s">
         <v>30</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>31</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="H7" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="I7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" t="s">
         <v>34</v>
       </c>
-      <c r="E8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" t="s">
-        <v>35</v>
-      </c>
       <c r="I8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C9" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F9" s="1">
         <v>1</v>
       </c>
       <c r="G9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="I9" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="10" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C10" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C11" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="F11" s="1">
         <v>1</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="12" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C12" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C13" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F13" s="1">
         <v>1</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
